--- a/campanhas/tabela-precos-cliente-outubro-2026/tabela-precos-black-november-2026-10-23.xlsx
+++ b/campanhas/tabela-precos-cliente-outubro-2026/tabela-precos-black-november-2026-10-23.xlsx
@@ -453,10 +453,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -515,7 +515,7 @@
         <v>599</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>599</v>
+        <v>539.1</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>246</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>246</v>
+        <v>221.4</v>
       </c>
     </row>
     <row r="6">
@@ -557,7 +557,7 @@
         <v>229</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>229</v>
+        <v>206.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,90 +578,237 @@
         <v>178</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>178</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>A d'Aussières Rouge 2023</t>
+          <t>Langhe Nebbiolo Reggimento 2020</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Domaine d'Aussières</t>
+          <t>Ratti</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>219</v>
+        <v>559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>186.15</v>
+        <v>475.15</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>167.54</v>
+        <v>427.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Gualta Malbec 2022</t>
+          <t>Preludio Barrel Select 2023 (branco)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Michelini i Mufatto</t>
+          <t>Familia Deicas</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>199</v>
+        <v>439</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>169.15</v>
+        <v>373.15</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>152.24</v>
+        <v>335.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Balsa de Piedra Semillon 2023</t>
+          <t>Extreme Vineyard Suelo Invertido Tannat 2021</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Michelini i Mufatto</t>
+          <t>Familia Deicas</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>179</v>
+        <v>399</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>152.15</v>
+        <v>339.15</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>136.94</v>
+        <v>305.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Pequeñas Producciones Malbec 2021</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Escorihuela Gascón</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>262.65</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>236.39</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Langhe Nebbiolo 2023</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Castello di Verduno</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>245.65</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>221.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Langhe Nebbiolo 2021</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Fontanafredda</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>237.15</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>213.44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>A d'Aussières Rouge 2023</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Domaine d'Aussières</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>186.15</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>167.54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gualta Malbec 2022</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Michelini i Mufatto</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>169.15</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>152.24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Balsa de Piedra Semillon 2023 (branco)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Michelini i Mufatto</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>152.15</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>136.94</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Espumante Blanc de Noir Brut</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Don Giovanni</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>152.15</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>136.94</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Espumante Stravaganzza Brut</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Don Giovanni</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>118.15</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E18" s="6" t="n">
         <v>106.34</v>
       </c>
     </row>

--- a/campanhas/tabela-precos-cliente-outubro-2026/tabela-precos-black-november-2026-10-23.xlsx
+++ b/campanhas/tabela-precos-cliente-outubro-2026/tabela-precos-black-november-2026-10-23.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -515,7 +515,7 @@
         <v>599</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>539.1</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>246</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>221.4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
@@ -557,7 +557,7 @@
         <v>229</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>206.1</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>178</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>160.2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
@@ -596,10 +596,10 @@
         <v>559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>475.15</v>
+        <v>475</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>427.64</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -617,10 +617,10 @@
         <v>439</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>373.15</v>
+        <v>373</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>335.84</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -638,10 +638,10 @@
         <v>399</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>339.15</v>
+        <v>339</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>305.24</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -659,10 +659,10 @@
         <v>309</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>262.65</v>
+        <v>263</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>236.39</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
@@ -680,10 +680,10 @@
         <v>289</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>245.65</v>
+        <v>246</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>221.09</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13">
@@ -701,10 +701,10 @@
         <v>279</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>237.15</v>
+        <v>237</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>213.44</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
@@ -722,10 +722,10 @@
         <v>219</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>186.15</v>
+        <v>186</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>167.54</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
@@ -743,10 +743,10 @@
         <v>199</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>169.15</v>
+        <v>169</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>152.24</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
@@ -764,10 +764,10 @@
         <v>179</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>152.15</v>
+        <v>152</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>136.94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -785,10 +785,10 @@
         <v>179</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>152.15</v>
+        <v>152</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>136.94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
@@ -806,10 +806,10 @@
         <v>139</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>118.15</v>
+        <v>118</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>106.34</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
